--- a/SS3 models/PRZO/06_Base_Final/bootstrap/01_tables.xlsx
+++ b/SS3 models/PRZO/06_Base_Final/bootstrap/01_tables.xlsx
@@ -6,15 +6,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="01_Quants" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_RefPoints" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Sensitivies" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_Quants" sheetId="7" state="visible" r:id="rId1"/>
+    <sheet name="02_RefPoints" sheetId="8" state="visible" r:id="rId2"/>
+    <sheet name="03_Sensitivies" sheetId="9" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -608,6 +608,42 @@
   </si>
   <si>
     <t xml:space="preserve">0.99 (0.99 - 0.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 (0.001 - 0.006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025/Fmsy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012 (0.007 - 0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26 (1.67 - 2.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025/SSBmsst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62 (3.36 - 3.83)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch_2023-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (0.01 - 0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98 (0.98 - 0.98)</t>
   </si>
 </sst>
 </file>
@@ -2305,18 +2341,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -2329,18 +2365,18 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
@@ -2353,10 +2389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -2369,10 +2405,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
